--- a/template/6.11/量化业务日报-2025-06-11.xlsx
+++ b/template/6.11/量化业务日报-2025-06-11.xlsx
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>0.99679</v>
+        <v>0.99692</v>
       </c>
       <c r="C18" s="4" t="n"/>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>0.013%</t>
+          <t>-4e-05%</t>
         </is>
       </c>
       <c r="C20" s="4" t="n"/>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>0.99679</v>
+        <v>0.99692</v>
       </c>
       <c r="C20" s="4" t="n"/>
     </row>
@@ -1376,7 +1376,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>0.013%</t>
+          <t>-4e-05%</t>
         </is>
       </c>
       <c r="C22" s="4" t="n"/>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>1.00005</v>
+        <v>0.99424</v>
       </c>
     </row>
     <row r="15" ht="27" customHeight="1">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>-0.58104%</t>
+          <t>-7e-05%</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>1.00005</v>
+        <v>0.9959</v>
       </c>
     </row>
     <row r="15" ht="27" customHeight="1">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>-0.41537%</t>
+          <t>-0.00039%</t>
         </is>
       </c>
     </row>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>1.00005</v>
+        <v>1.0001</v>
       </c>
     </row>
     <row r="15" ht="27" customHeight="1">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>0.00489%</t>
+          <t>-0.00011%</t>
         </is>
       </c>
     </row>
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>1.00005</v>
+        <v>1.0001</v>
       </c>
     </row>
     <row r="15" ht="27" customHeight="1">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>0.00488%</t>
+          <t>-0.00012%</t>
         </is>
       </c>
     </row>
